--- a/config/generated/templates/SnapshotCapture.xlsx
+++ b/config/generated/templates/SnapshotCapture.xlsx
@@ -751,8 +751,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Stat, Resource, StateSlot, Expression" promptTitle="SnapshotCaptureKind enum" prompt="Select a value from the dropdown." sqref="F8:F1007">
       <formula1>"Stat,Resource,StateSlot,Expression"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Hp, Atk, Def, Spd, CritRate, CritDamage, EffectHitRate, EffectResistance, BreakEffect, EnergyRegenerationRate, OutgoingHealing, IncomingHealing, ShieldStrength, Aggro, ToughnessDamage" promptTitle="StatKind enum" prompt="Select a value from the dropdown." sqref="G8:G1007">
-      <formula1>"Hp,Atk,Def,Spd,CritRate,CritDamage,EffectHitRate,EffectResistance,BreakEffect,EnergyRegenerationRate,OutgoingHealing,IncomingHealing,ShieldStrength,Aggro,ToughnessDamage"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Hp, Atk, Def, Spd, CritRate, CritDamage, EffectHitRate, EffectResistance, BreakEffect, EnergyRegenerationRate, OutgoingHealing, IncomingHealing, ShieldStrength, Aggro, ToughnessDamage, Elation" promptTitle="StatKind enum" prompt="Select a value from the dropdown." sqref="G8:G1007">
+      <formula1>"Hp,Atk,Def,Spd,CritRate,CritDamage,EffectHitRate,EffectResistance,BreakEffect,EnergyRegenerationRate,OutgoingHealing,IncomingHealing,ShieldStrength,Aggro,ToughnessDamage,Elation"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Energy, SkillPoints, Hp, CharacterResource, TeamResource" promptTitle="ResourceKind enum" prompt="Select a value from the dropdown." sqref="H8:H1007">
       <formula1>"Energy,SkillPoints,Hp,CharacterResource,TeamResource"</formula1>
